--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -1655,10 +1655,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118755471</v>
+        <v>118756349</v>
       </c>
       <c r="B10" t="n">
-        <v>5165</v>
+        <v>57240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,47 +1667,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102204</v>
+        <v>102621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kjolgran Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 3 NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>344126</v>
+        <v>343970</v>
       </c>
       <c r="R10" t="n">
-        <v>6434123</v>
+        <v>6434151</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1739,7 +1742,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1749,7 +1752,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1758,7 +1761,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1777,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118756349</v>
+        <v>118755471</v>
       </c>
       <c r="B11" t="n">
-        <v>57240</v>
+        <v>5165</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,50 +1791,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>102204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog 3 NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>343970</v>
+        <v>344126</v>
       </c>
       <c r="R11" t="n">
-        <v>6434151</v>
+        <v>6434123</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1864,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1874,7 +1873,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,6 +1882,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -1655,10 +1655,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118756349</v>
+        <v>118756005</v>
       </c>
       <c r="B10" t="n">
-        <v>57240</v>
+        <v>57443</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,25 +1667,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102621</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118755471</v>
+        <v>118756349</v>
       </c>
       <c r="B11" t="n">
-        <v>5165</v>
+        <v>57240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1791,47 +1791,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102204</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kjolgran Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 3 NO Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>344126</v>
+        <v>343970</v>
       </c>
       <c r="R11" t="n">
-        <v>6434123</v>
+        <v>6434151</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1863,7 +1866,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,7 +1876,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1882,7 +1885,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1901,10 +1903,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118756005</v>
+        <v>118755471</v>
       </c>
       <c r="B12" t="n">
-        <v>57443</v>
+        <v>5165</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1917,46 +1919,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>102204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skog 3 NO Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>343970</v>
+        <v>344126</v>
       </c>
       <c r="R12" t="n">
-        <v>6434151</v>
+        <v>6434123</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1988,7 +1987,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1998,7 +1997,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2007,6 +2006,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2281,6 +2281,615 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120391586</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5168</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>344100</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6434190</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120392243</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57996</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>344145</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6434209</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120392273</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56532</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>344145</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6434209</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120391450</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5168</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kjolgran 2 Ö Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>344122</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6434110</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120392392</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skog 4 V Bredmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>344139</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6434208</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2283,7 +2283,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120391586</v>
+        <v>120391450</v>
       </c>
       <c r="B15" t="n">
         <v>5168</v>
@@ -2328,14 +2328,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 2 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>344100</v>
+        <v>344122</v>
       </c>
       <c r="R15" t="n">
-        <v>6434190</v>
+        <v>6434110</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2525,10 +2525,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120392273</v>
+        <v>120392392</v>
       </c>
       <c r="B17" t="n">
-        <v>56532</v>
+        <v>57326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2537,25 +2537,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,20 +2563,20 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+          <t>Skog 4 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>344145</v>
+        <v>344139</v>
       </c>
       <c r="R17" t="n">
-        <v>6434209</v>
+        <v>6434208</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2618,12 +2618,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2650,10 +2645,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120391450</v>
+        <v>120392273</v>
       </c>
       <c r="B18" t="n">
-        <v>5168</v>
+        <v>56532</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2662,47 +2657,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102204</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kjolgran 2 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>344122</v>
+        <v>344145</v>
       </c>
       <c r="R18" t="n">
-        <v>6434110</v>
+        <v>6434209</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2734,7 +2728,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2744,7 +2738,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,7 +2752,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2772,10 +2770,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120392392</v>
+        <v>120391586</v>
       </c>
       <c r="B19" t="n">
-        <v>57326</v>
+        <v>5168</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2788,42 +2786,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100048</v>
+        <v>102204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skog 4 V Bredmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>344139</v>
+        <v>344100</v>
       </c>
       <c r="R19" t="n">
-        <v>6434208</v>
+        <v>6434190</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2855,7 +2854,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2865,7 +2864,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2874,6 +2873,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2405,10 +2405,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120392243</v>
+        <v>120392392</v>
       </c>
       <c r="B16" t="n">
-        <v>57996</v>
+        <v>57326</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2417,20 +2417,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103044</v>
+        <v>100048</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2449,14 +2449,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+          <t>Skog 4 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>344145</v>
+        <v>344139</v>
       </c>
       <c r="R16" t="n">
-        <v>6434209</v>
+        <v>6434208</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2525,10 +2525,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120392392</v>
+        <v>120392273</v>
       </c>
       <c r="B17" t="n">
-        <v>57326</v>
+        <v>56532</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2537,25 +2537,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,20 +2563,20 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skog 4 V Bredmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>344139</v>
+        <v>344145</v>
       </c>
       <c r="R17" t="n">
-        <v>6434208</v>
+        <v>6434209</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2618,7 +2618,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,10 +2650,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120392273</v>
+        <v>120391586</v>
       </c>
       <c r="B18" t="n">
-        <v>56532</v>
+        <v>5168</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2657,46 +2662,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>102204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>344145</v>
+        <v>344100</v>
       </c>
       <c r="R18" t="n">
-        <v>6434209</v>
+        <v>6434190</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2728,7 +2734,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2738,12 +2744,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2752,6 +2753,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2770,10 +2772,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120391586</v>
+        <v>120392243</v>
       </c>
       <c r="B19" t="n">
-        <v>5168</v>
+        <v>57996</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2782,47 +2784,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102204</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>344100</v>
+        <v>344145</v>
       </c>
       <c r="R19" t="n">
-        <v>6434190</v>
+        <v>6434209</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2854,7 +2855,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2864,7 +2865,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2873,7 +2874,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2283,10 +2283,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120391450</v>
+        <v>120392273</v>
       </c>
       <c r="B15" t="n">
-        <v>5168</v>
+        <v>56532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2295,47 +2295,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102204</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kjolgran 2 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>344122</v>
+        <v>344145</v>
       </c>
       <c r="R15" t="n">
-        <v>6434110</v>
+        <v>6434209</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2367,7 +2366,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2377,7 +2376,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2386,7 +2390,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2525,10 +2528,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120392273</v>
+        <v>120392243</v>
       </c>
       <c r="B17" t="n">
-        <v>56532</v>
+        <v>57996</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2541,21 +2544,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,7 +2566,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2608,7 +2611,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2618,12 +2621,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2650,7 +2648,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120391586</v>
+        <v>120391450</v>
       </c>
       <c r="B18" t="n">
         <v>5168</v>
@@ -2695,14 +2693,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 2 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>344100</v>
+        <v>344122</v>
       </c>
       <c r="R18" t="n">
-        <v>6434190</v>
+        <v>6434110</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2734,7 +2732,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2744,7 +2742,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2772,10 +2770,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120392243</v>
+        <v>120391586</v>
       </c>
       <c r="B19" t="n">
-        <v>57996</v>
+        <v>5168</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2784,46 +2782,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>102204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>344145</v>
+        <v>344100</v>
       </c>
       <c r="R19" t="n">
-        <v>6434209</v>
+        <v>6434190</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2855,7 +2854,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2865,7 +2864,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2874,6 +2873,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2283,10 +2283,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120392273</v>
+        <v>120392243</v>
       </c>
       <c r="B15" t="n">
-        <v>56532</v>
+        <v>57996</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2321,7 +2321,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2376,12 +2376,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2408,10 +2403,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120392392</v>
+        <v>120391450</v>
       </c>
       <c r="B16" t="n">
-        <v>57326</v>
+        <v>5168</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2424,42 +2419,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100048</v>
+        <v>102204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skog 4 V Bredmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 2 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>344139</v>
+        <v>344122</v>
       </c>
       <c r="R16" t="n">
-        <v>6434208</v>
+        <v>6434110</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2491,7 +2487,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2501,7 +2497,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2510,6 +2506,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2528,10 +2525,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120392243</v>
+        <v>120392392</v>
       </c>
       <c r="B17" t="n">
-        <v>57996</v>
+        <v>57326</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2540,20 +2537,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103044</v>
+        <v>100048</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2572,14 +2569,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+          <t>Skog 4 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>344145</v>
+        <v>344139</v>
       </c>
       <c r="R17" t="n">
-        <v>6434209</v>
+        <v>6434208</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2611,7 +2608,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2621,7 +2618,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2648,7 +2645,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120391450</v>
+        <v>120391586</v>
       </c>
       <c r="B18" t="n">
         <v>5168</v>
@@ -2693,14 +2690,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kjolgran 2 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>344122</v>
+        <v>344100</v>
       </c>
       <c r="R18" t="n">
-        <v>6434110</v>
+        <v>6434190</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2732,7 +2729,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2742,7 +2739,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2770,10 +2767,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120391586</v>
+        <v>120392273</v>
       </c>
       <c r="B19" t="n">
-        <v>5168</v>
+        <v>56532</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2782,47 +2779,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102204</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>344100</v>
+        <v>344145</v>
       </c>
       <c r="R19" t="n">
-        <v>6434190</v>
+        <v>6434209</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2854,7 +2850,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2864,7 +2860,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2873,7 +2874,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2283,10 +2283,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120392243</v>
+        <v>120391586</v>
       </c>
       <c r="B15" t="n">
-        <v>57996</v>
+        <v>5168</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2295,46 +2295,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103044</v>
+        <v>102204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>344145</v>
+        <v>344100</v>
       </c>
       <c r="R15" t="n">
-        <v>6434209</v>
+        <v>6434190</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2366,7 +2367,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2376,7 +2377,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2385,6 +2386,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2403,10 +2405,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120391450</v>
+        <v>120392392</v>
       </c>
       <c r="B16" t="n">
-        <v>5168</v>
+        <v>57326</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2419,43 +2421,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102204</v>
+        <v>100048</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kjolgran 2 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 4 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>344122</v>
+        <v>344139</v>
       </c>
       <c r="R16" t="n">
-        <v>6434110</v>
+        <v>6434208</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2487,7 +2488,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2497,7 +2498,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2506,7 +2507,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120392392</v>
+        <v>120392273</v>
       </c>
       <c r="B17" t="n">
-        <v>57326</v>
+        <v>56532</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2537,25 +2537,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2563,20 +2563,20 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skog 4 V Bredmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>344139</v>
+        <v>344145</v>
       </c>
       <c r="R17" t="n">
-        <v>6434208</v>
+        <v>6434209</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2618,7 +2618,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,7 +2650,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120391586</v>
+        <v>120391450</v>
       </c>
       <c r="B18" t="n">
         <v>5168</v>
@@ -2690,14 +2695,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kjolgran 3 Ö Ledningsmossen, Drängedalen, Vg</t>
+          <t>Kjolgran 2 Ö Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>344100</v>
+        <v>344122</v>
       </c>
       <c r="R18" t="n">
-        <v>6434190</v>
+        <v>6434110</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2729,7 +2734,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2739,7 +2744,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2767,10 +2772,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120392273</v>
+        <v>120392243</v>
       </c>
       <c r="B19" t="n">
-        <v>56532</v>
+        <v>57996</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2783,21 +2788,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2805,7 +2810,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2850,7 +2855,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2860,12 +2865,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fjäder från tjäderhöna. Vid stenhäll.</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2286,7 +2286,7 @@
         <v>120392392</v>
       </c>
       <c r="B15" t="n">
-        <v>57341</v>
+        <v>57493</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skog 4 V Bredmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>344139</v>
+        <v>344145</v>
       </c>
       <c r="R15" t="n">
-        <v>6434208</v>
+        <v>6434209</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2890,6 +2890,889 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123819568</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57640</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>344145</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6434209</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123819691</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58165</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>344031</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6434118</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst tre, full rulle.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123819702</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58165</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>344119</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6434098</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Flera, full rulle.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123819892</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>344031</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6434118</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hördes söderifrån ropa i denna riktning.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123819704</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56697</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>344119</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6434098</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning på två stubbar i hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123819585</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58347</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Körspår på hygge Ö om Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>344129</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6433972</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I vattenfyllt körspår på hygget.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123819701</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57857</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>344119</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6434098</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ola Freijd</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2286,7 +2286,7 @@
         <v>120392392</v>
       </c>
       <c r="B15" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123819568</v>
+        <v>123819704</v>
       </c>
       <c r="B20" t="n">
-        <v>57640</v>
+        <v>56700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2904,50 +2904,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>344145</v>
+        <v>344119</v>
       </c>
       <c r="R20" t="n">
-        <v>6434209</v>
+        <v>6434098</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2974,22 +2970,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spillning på två stubbar i hyggeskant.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3016,10 +3017,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123819691</v>
+        <v>123819892</v>
       </c>
       <c r="B21" t="n">
-        <v>58165</v>
+        <v>57506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3028,20 +3029,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3049,7 +3050,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
@@ -3099,7 +3104,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3109,12 +3114,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst tre, full rulle.</t>
+          <t>Hördes söderifrån ropa i denna riktning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3141,10 +3146,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123819702</v>
+        <v>123819568</v>
       </c>
       <c r="B22" t="n">
-        <v>58165</v>
+        <v>57643</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3153,46 +3158,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>344119</v>
+        <v>344145</v>
       </c>
       <c r="R22" t="n">
-        <v>6434098</v>
+        <v>6434209</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3219,27 +3228,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Flera, full rulle.</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3266,10 +3270,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819892</v>
+        <v>123819701</v>
       </c>
       <c r="B23" t="n">
-        <v>57506</v>
+        <v>57860</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3278,20 +3282,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3308,20 +3312,20 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>344031</v>
+        <v>344119</v>
       </c>
       <c r="R23" t="n">
-        <v>6434118</v>
+        <v>6434098</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3353,7 +3357,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3363,12 +3367,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hördes söderifrån ropa i denna riktning.</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3395,10 +3394,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819704</v>
+        <v>123819585</v>
       </c>
       <c r="B24" t="n">
-        <v>56697</v>
+        <v>58350</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3411,16 +3410,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>208249</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3428,25 +3427,30 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Körspår på hygge Ö om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>344119</v>
+        <v>344129</v>
       </c>
       <c r="R24" t="n">
-        <v>6434098</v>
+        <v>6433972</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3473,27 +3477,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Spillning på två stubbar i hyggeskant.</t>
+          <t>I vattenfyllt körspår på hygget.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3502,6 +3506,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3520,10 +3525,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123819585</v>
+        <v>123819702</v>
       </c>
       <c r="B25" t="n">
-        <v>58347</v>
+        <v>58168</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3536,47 +3541,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208249</v>
+        <v>103044</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Körspår på hygge Ö om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>344129</v>
+        <v>344119</v>
       </c>
       <c r="R25" t="n">
-        <v>6433972</v>
+        <v>6434098</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3603,27 +3603,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I vattenfyllt körspår på hygget.</t>
+          <t>Flera, full rulle.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3632,7 +3632,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3651,10 +3650,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123819701</v>
+        <v>123819691</v>
       </c>
       <c r="B26" t="n">
-        <v>57857</v>
+        <v>58168</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3667,16 +3666,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3684,29 +3683,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>344119</v>
+        <v>344031</v>
       </c>
       <c r="R26" t="n">
-        <v>6434098</v>
+        <v>6434118</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3738,7 +3733,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3748,7 +3743,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst tre, full rulle.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2286,7 +2286,7 @@
         <v>120392392</v>
       </c>
       <c r="B15" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123819704</v>
+        <v>123819702</v>
       </c>
       <c r="B20" t="n">
-        <v>56700</v>
+        <v>58169</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Spillning på två stubbar i hyggeskant.</t>
+          <t>Flera, full rulle.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3020,7 +3020,7 @@
         <v>123819892</v>
       </c>
       <c r="B21" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123819568</v>
+        <v>123819701</v>
       </c>
       <c r="B22" t="n">
-        <v>57643</v>
+        <v>57861</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3158,25 +3158,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3188,20 +3188,20 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>344145</v>
+        <v>344119</v>
       </c>
       <c r="R22" t="n">
-        <v>6434209</v>
+        <v>6434098</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3228,22 +3228,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3270,10 +3270,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819701</v>
+        <v>123819704</v>
       </c>
       <c r="B23" t="n">
-        <v>57860</v>
+        <v>56700</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3286,33 +3286,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3368,6 +3364,11 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillning på två stubbar i hyggeskant.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3397,7 +3398,7 @@
         <v>123819585</v>
       </c>
       <c r="B24" t="n">
-        <v>58350</v>
+        <v>58351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3525,10 +3526,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123819702</v>
+        <v>123819568</v>
       </c>
       <c r="B25" t="n">
-        <v>58168</v>
+        <v>57644</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3537,46 +3538,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>344119</v>
+        <v>344145</v>
       </c>
       <c r="R25" t="n">
-        <v>6434098</v>
+        <v>6434209</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3603,27 +3608,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Flera, full rulle.</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3653,7 +3653,7 @@
         <v>123819691</v>
       </c>
       <c r="B26" t="n">
-        <v>58168</v>
+        <v>58169</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2892,10 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123819704</v>
+        <v>123819691</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>58191</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2930,20 +2930,20 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>344119</v>
+        <v>344031</v>
       </c>
       <c r="R20" t="n">
-        <v>6434098</v>
+        <v>6434118</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Spillning på två stubbar i hyggeskant.</t>
+          <t>Minst tre, full rulle.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3148,10 +3148,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123819702</v>
+        <v>123819704</v>
       </c>
       <c r="B22" t="n">
-        <v>58191</v>
+        <v>56722</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3164,21 +3164,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3186,7 +3186,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flera, full rulle.</t>
+          <t>Spillning på två stubbar i hyggeskant.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3273,10 +3273,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819701</v>
+        <v>123819892</v>
       </c>
       <c r="B23" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3285,20 +3285,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3315,20 +3315,20 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>344119</v>
+        <v>344031</v>
       </c>
       <c r="R23" t="n">
-        <v>6434098</v>
+        <v>6434118</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3370,7 +3370,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hördes söderifrån ropa i denna riktning.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3397,10 +3402,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819568</v>
+        <v>123819702</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>58191</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3409,50 +3414,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>344145</v>
+        <v>344119</v>
       </c>
       <c r="R24" t="n">
-        <v>6434209</v>
+        <v>6434098</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3479,22 +3480,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flera, full rulle.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3521,10 +3527,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123819892</v>
+        <v>123819701</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3533,20 +3539,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3563,20 +3569,20 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>344031</v>
+        <v>344119</v>
       </c>
       <c r="R25" t="n">
-        <v>6434118</v>
+        <v>6434098</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3608,7 +3614,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3618,12 +3624,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>07:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hördes söderifrån ropa i denna riktning.</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3650,10 +3651,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123819691</v>
+        <v>123819568</v>
       </c>
       <c r="B26" t="n">
-        <v>58191</v>
+        <v>57666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3662,46 +3663,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>344031</v>
+        <v>344145</v>
       </c>
       <c r="R26" t="n">
-        <v>6434118</v>
+        <v>6434209</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3728,27 +3733,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst tre, full rulle.</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2892,10 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123819691</v>
+        <v>123819892</v>
       </c>
       <c r="B20" t="n">
-        <v>58191</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2904,20 +2904,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2925,7 +2925,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
@@ -2975,7 +2979,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2985,12 +2989,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst tre, full rulle.</t>
+          <t>Hördes söderifrån ropa i denna riktning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3017,10 +3021,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123819585</v>
+        <v>123819701</v>
       </c>
       <c r="B21" t="n">
-        <v>58373</v>
+        <v>57883</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3033,21 +3037,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208249</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3055,25 +3059,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Körspår på hygge Ö om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>344129</v>
+        <v>344119</v>
       </c>
       <c r="R21" t="n">
-        <v>6433972</v>
+        <v>6434098</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3100,27 +3103,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>I vattenfyllt körspår på hygget.</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3129,7 +3127,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3148,10 +3145,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123819704</v>
+        <v>123819702</v>
       </c>
       <c r="B22" t="n">
-        <v>56722</v>
+        <v>58191</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3164,21 +3161,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3186,7 +3183,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3246,7 +3243,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Spillning på två stubbar i hyggeskant.</t>
+          <t>Flera, full rulle.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3273,10 +3270,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123819892</v>
+        <v>123819585</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>58373</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3285,25 +3282,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>208249</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3311,24 +3308,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
+          <t>Körspår på hygge Ö om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>344031</v>
+        <v>344129</v>
       </c>
       <c r="R23" t="n">
-        <v>6434118</v>
+        <v>6433972</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3355,27 +3353,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hördes söderifrån ropa i denna riktning.</t>
+          <t>I vattenfyllt körspår på hygget.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3384,6 +3382,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3402,10 +3401,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819702</v>
+        <v>123819704</v>
       </c>
       <c r="B24" t="n">
-        <v>58191</v>
+        <v>56722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3418,21 +3417,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3440,7 +3439,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3500,7 +3499,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Flera, full rulle.</t>
+          <t>Spillning på två stubbar i hyggeskant.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3527,10 +3526,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123819701</v>
+        <v>123819568</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3539,25 +3538,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3569,20 +3568,20 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>344119</v>
+        <v>344145</v>
       </c>
       <c r="R25" t="n">
-        <v>6434098</v>
+        <v>6434209</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3609,22 +3608,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3651,10 +3650,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123819568</v>
+        <v>123819691</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>58191</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3663,50 +3662,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skog 2 V Bredmossen, Drängedalen, Vg</t>
+          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>344145</v>
+        <v>344031</v>
       </c>
       <c r="R26" t="n">
-        <v>6434209</v>
+        <v>6434118</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3733,22 +3728,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025-03-09</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst tre, full rulle.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 53693-2019 artfynd.xlsx
+++ b/artfynd/A 53693-2019 artfynd.xlsx
@@ -2892,10 +2892,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123819892</v>
+        <v>123819691</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>58191</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2904,20 +2904,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2925,11 +2925,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
@@ -2979,7 +2975,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2989,12 +2985,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hördes söderifrån ropa i denna riktning.</t>
+          <t>Minst tre, full rulle.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3021,10 +3017,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123819701</v>
+        <v>123819892</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3033,20 +3029,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3063,20 +3059,20 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>344119</v>
+        <v>344031</v>
       </c>
       <c r="R21" t="n">
-        <v>6434098</v>
+        <v>6434118</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3108,7 +3104,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3118,7 +3114,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hördes söderifrån ropa i denna riktning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3145,10 +3146,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123819702</v>
+        <v>123819701</v>
       </c>
       <c r="B22" t="n">
-        <v>58191</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3161,16 +3162,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3178,12 +3179,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3239,11 +3244,6 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Flera, full rulle.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3401,10 +3401,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123819704</v>
+        <v>123819702</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
+        <v>58191</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3417,21 +3417,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>103044</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3439,7 +3439,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Spillning på två stubbar i hyggeskant.</t>
+          <t>Flera, full rulle.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3650,10 +3650,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123819691</v>
+        <v>123819704</v>
       </c>
       <c r="B26" t="n">
-        <v>58191</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3666,21 +3666,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3688,20 +3688,20 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skog O Ledningsmossen, Drängedalen, Vg</t>
+          <t>Skogskant mot hygge, Ö om Ledningsmossen, Drängedalen, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>344031</v>
+        <v>344119</v>
       </c>
       <c r="R26" t="n">
-        <v>6434118</v>
+        <v>6434098</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst tre, full rulle.</t>
+          <t>Spillning på två stubbar i hyggeskant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
